--- a/rtos-api-analysis/results/threadx-5.3_vulnerability_report.xlsx
+++ b/rtos-api-analysis/results/threadx-5.3_vulnerability_report.xlsx
@@ -32286,9 +32286,9 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_delete.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_delete.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_delete.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -32298,11 +32298,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -32331,11 +32331,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_front_send.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_front_send.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -32345,13 +32345,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -32414,8 +32414,8 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_info_get.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -32425,9 +32425,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -32459,8 +32459,8 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -32470,13 +32470,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -32512,8 +32512,8 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>runtime/Freestanding/memset.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_create.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_create.c
+runtime/Freestanding/memset.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -32524,8 +32524,8 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -32551,9 +32551,9 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send_notify.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send_notify.c
 /home/klee/klee_src//threadx_test/evaluation_files/queue_send_notify.c</t>
         </is>
       </c>
@@ -32564,11 +32564,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -32597,9 +32597,9 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_terminate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_terminate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_terminate.c</t>
         </is>
       </c>
@@ -32610,12 +32610,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -32671,8 +32671,8 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_release.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_release.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -32682,9 +32682,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
-Pointer Out of Bound
-Uninitialized pointer dereference(read) vulnerability</t>
+          <t>Uninitialized pointer dereference(read) vulnerability
+Information leak vulnerability (limited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -32713,9 +32713,9 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
 Pointer Out of Bound
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -32747,8 +32747,8 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_info_get.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -32758,9 +32758,9 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -32818,8 +32818,8 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_prioritize.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -32829,10 +32829,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -32866,10 +32866,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -32902,10 +32902,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Uninitialized pointer dereference(read) vulnerability
 Information leak vulnerability (limited)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -32930,10 +32930,10 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_allocate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_allocate.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_allocate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_allocate.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -32943,10 +32943,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
-Pointer Out of Bound
+          <t>Limited memory write vulnerability (V1)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -32976,11 +32976,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -32990,12 +32990,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -33050,10 +33050,10 @@
       <c r="A18" t="inlineStr">
         <is>
           <t>runtime/Freestanding/memset.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_create.c
 /home/klee/klee_src//threadx_test/evaluation_files/timer_create.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_create.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -33063,12 +33063,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arbitrary memory write vulnerability (V0)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
+Arbitrary memory write vulnerability (V0)
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -33111,10 +33111,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src//threadx_test/evaluation_files/thread_create.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/src/txm_module_manager_thread_create.c
 runtime/Freestanding/memset.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/src/txm_module_manager_thread_create.c</t>
+/home/klee/klee_src//threadx_test/evaluation_files/thread_create.c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -33125,9 +33125,9 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Uninitialized pointer dereference(read) vulnerability
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -33216,10 +33216,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -33241,11 +33241,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_put.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -33255,11 +33255,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -33327,10 +33327,10 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_get.c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -33340,10 +33340,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
-Pointer Out of Bound
+          <t>Limited memory write vulnerability (V1)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -33370,8 +33370,8 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_time_slice_change.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_time_slice_change.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_time_slice_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_time_slice_change.c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -33381,12 +33381,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -33412,10 +33412,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_wait_abort.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_wait_abort.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_wait_abort.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -33425,12 +33425,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -33512,10 +33512,10 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_entry_exit_notify.c
-/home/klee/klee_src//threadx_test/evaluation_files/thread_entry_exit_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_entry_exit_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_entry_exit_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_entry_exit_notify.c
+/home/klee/klee_src//threadx_test/evaluation_files/thread_entry_exit_notify.c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -33525,11 +33525,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -33551,8 +33551,8 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_prioritize.c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -33562,10 +33562,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -33589,8 +33589,8 @@
       <c r="A27" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -33600,11 +33600,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -33634,8 +33634,8 @@
       <c r="A28" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_allocate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_search.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_allocate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_allocate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_search.c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -33645,12 +33645,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -33690,12 +33690,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_delete.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -33705,11 +33705,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -33798,10 +33798,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -33835,10 +33835,10 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -33861,9 +33861,9 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_delete.c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -33873,11 +33873,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -33918,8 +33918,8 @@
       <c r="C33" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -33943,11 +33943,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_receive.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_receive.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_receive.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -33957,11 +33957,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -34029,9 +34029,9 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_ceiling_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_ceiling_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_ceiling_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_ceiling_put.c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -34041,13 +34041,13 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -34084,9 +34084,9 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -34096,11 +34096,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -34129,8 +34129,8 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_info_get.c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -34140,9 +34140,9 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -34175,9 +34175,9 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_resume.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
@@ -34188,11 +34188,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -34269,8 +34269,8 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -34296,8 +34296,8 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_prioritize.c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -34307,10 +34307,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -34333,8 +34333,8 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_info_get.c</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -34344,9 +34344,9 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -34376,10 +34376,10 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put_notify.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
 /home/klee/klee_src//threadx_test/evaluation_files/semaphore_put_notify.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put_notify.c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -34389,11 +34389,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -34433,10 +34433,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
 Information leak vulnerability (limited)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -34474,8 +34474,8 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_info_get.c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -34485,9 +34485,9 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -34520,9 +34520,9 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_suspend.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_suspend.c</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -34532,11 +34532,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -34587,9 +34587,9 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -34622,10 +34622,10 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src//threadx_test/evaluation_files/event_flags_set_notify.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set_notify.c
+/home/klee/klee_src//threadx_test/evaluation_files/event_flags_set_notify.c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -34635,11 +34635,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -34668,8 +34668,8 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_preemption_change.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_preemption_change.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_preemption_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_preemption_change.c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -34679,13 +34679,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -34722,8 +34722,8 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_release.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_release.c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -34733,8 +34733,8 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pointer Out of Bound
-Uninitialized pointer dereference(read) vulnerability</t>
+          <t>Uninitialized pointer dereference(read) vulnerability
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -34750,10 +34750,10 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_priority_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_priority_change.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_priority_change.c</t>
         </is>
       </c>
@@ -34764,13 +34764,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -34883,9 +34883,9 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_activate.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_activate.c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -34895,12 +34895,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -34947,11 +34947,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -35000,9 +35000,9 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -35041,10 +35041,10 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_get.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -35054,12 +35054,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -35119,10 +35119,10 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
-Pointer Out of Bound
+          <t>Pointer Out of Bound
+Arbitrary memory write vulnerability (V0)
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Arbitrary memory write vulnerability (V0)
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -35162,9 +35162,9 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_flush.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_flush.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_flush.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_flush.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -35174,12 +35174,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -35220,9 +35220,9 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -35232,13 +35232,13 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -35312,9 +35312,9 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_get.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_get.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_get.c</t>
         </is>
       </c>
@@ -35325,13 +35325,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -35384,9 +35384,9 @@
       <c r="C59" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
+Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -35426,8 +35426,8 @@
       <c r="A60" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -35437,11 +35437,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -35470,9 +35470,9 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -35482,10 +35482,10 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -35568,9 +35568,9 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_delete.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_delete.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_delete.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -35580,11 +35580,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -35628,11 +35628,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_front_send.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_front_send.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -35642,13 +35642,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -35726,8 +35726,8 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_info_get.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -35737,9 +35737,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -35786,8 +35786,8 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -35797,13 +35797,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -35854,8 +35854,8 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>runtime/Freestanding/memset.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_create.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_create.c
+runtime/Freestanding/memset.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -35866,8 +35866,8 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -35901,16 +35901,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send_notify.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send_notify.c
 /home/klee/klee_src//threadx_test/evaluation_files/queue_send_notify.c</t>
         </is>
       </c>
@@ -35921,11 +35921,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -35969,9 +35969,9 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_terminate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_terminate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_terminate.c</t>
         </is>
       </c>
@@ -35982,12 +35982,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -36058,8 +36058,8 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_release.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_release.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -36069,9 +36069,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
-Pointer Out of Bound
-Uninitialized pointer dereference(read) vulnerability</t>
+          <t>Uninitialized pointer dereference(read) vulnerability
+Information leak vulnerability (limited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -36115,9 +36115,9 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
 Pointer Out of Bound
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -36157,15 +36157,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_info_get.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -36175,9 +36175,9 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -36225,8 +36225,8 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_prioritize.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -36236,10 +36236,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -36288,10 +36288,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -36339,10 +36339,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Uninitialized pointer dereference(read) vulnerability
 Information leak vulnerability (limited)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -36382,10 +36382,10 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_allocate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_allocate.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_allocate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_allocate.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -36395,10 +36395,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
-Pointer Out of Bound
+          <t>Limited memory write vulnerability (V1)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -36443,11 +36443,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_send.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_send.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -36457,12 +36457,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -36532,10 +36532,10 @@
       <c r="A17" t="inlineStr">
         <is>
           <t>runtime/Freestanding/memset.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_create.c
 /home/klee/klee_src//threadx_test/evaluation_files/timer_create.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_create.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -36545,12 +36545,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arbitrary memory write vulnerability (V0)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
+Arbitrary memory write vulnerability (V0)
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -36601,17 +36601,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src//threadx_test/evaluation_files/thread_create.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/src/txm_module_manager_thread_create.c
 runtime/Freestanding/memset.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/src/txm_module_manager_thread_create.c</t>
+/home/klee/klee_src//threadx_test/evaluation_files/thread_create.c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -36622,9 +36622,9 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Uninitialized pointer dereference(read) vulnerability
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -36710,7 +36710,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -36728,10 +36728,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -36768,11 +36768,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_put.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -36782,11 +36782,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -36869,10 +36869,10 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_get.c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -36882,10 +36882,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
-Pointer Out of Bound
+          <t>Limited memory write vulnerability (V1)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -36927,8 +36927,8 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_time_slice_change.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_time_slice_change.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_time_slice_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_time_slice_change.c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -36938,12 +36938,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -36984,10 +36984,10 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_wait_abort.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_wait_abort.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_wait_abort.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -36997,12 +36997,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -37099,10 +37099,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_entry_exit_notify.c
-/home/klee/klee_src//threadx_test/evaluation_files/thread_entry_exit_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_entry_exit_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_entry_exit_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_entry_exit_notify.c
+/home/klee/klee_src//threadx_test/evaluation_files/thread_entry_exit_notify.c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -37112,11 +37112,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -37153,8 +37153,8 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_prioritize.c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -37164,10 +37164,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -37206,8 +37206,8 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -37217,11 +37217,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -37266,8 +37266,8 @@
       <c r="A27" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_allocate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_search.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_allocate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_allocate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_search.c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -37277,12 +37277,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -37337,12 +37337,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_delete.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_prioritize.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -37352,11 +37352,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -37460,10 +37460,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -37512,10 +37512,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -37553,9 +37553,9 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_delete.c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -37565,11 +37565,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -37625,8 +37625,8 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -37658,18 +37658,18 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_receive.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_receive.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_receive.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -37679,11 +37679,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -37766,9 +37766,9 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_ceiling_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_ceiling_put.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_ceiling_put.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_ceiling_put.c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -37778,13 +37778,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -37836,9 +37836,9 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -37848,11 +37848,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -37896,8 +37896,8 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_info_get.c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -37907,9 +37907,9 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -37957,9 +37957,9 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_resume.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_resume.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
@@ -37970,11 +37970,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -38066,8 +38066,8 @@
       <c r="C38" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -38101,15 +38101,15 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_prioritize.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_prioritize.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_byte_pool_prioritize.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_byte_pool_prioritize.c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -38119,10 +38119,10 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -38160,8 +38160,8 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_info_get.c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -38171,9 +38171,9 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -38218,10 +38218,10 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put_notify.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
 /home/klee/klee_src//threadx_test/evaluation_files/semaphore_put_notify.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_put_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_put_notify.c</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -38231,11 +38231,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -38290,10 +38290,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
 Information leak vulnerability (limited)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -38346,8 +38346,8 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_info_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_info_get.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_pool_info_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_block_pool_info_get.c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -38357,9 +38357,9 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -38407,9 +38407,9 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_suspend.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_suspend.c</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -38419,11 +38419,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -38489,9 +38489,9 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -38539,10 +38539,10 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set_notify.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set_notify.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common_modules/module_manager/inc/txm_module_manager_dispatch.h
-/home/klee/klee_src//threadx_test/evaluation_files/event_flags_set_notify.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set_notify.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set_notify.c
+/home/klee/klee_src//threadx_test/evaluation_files/event_flags_set_notify.c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -38552,11 +38552,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
+Potential Function pointer dereference vulnerability
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -38600,8 +38600,8 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_preemption_change.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_preemption_change.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_preemption_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_preemption_change.c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -38611,13 +38611,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -38669,8 +38669,8 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_release.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_block_release.c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -38680,8 +38680,8 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pointer Out of Bound
-Uninitialized pointer dereference(read) vulnerability</t>
+          <t>Uninitialized pointer dereference(read) vulnerability
+Pointer Out of Bound</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -38712,10 +38712,10 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_priority_change.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_priority_change.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_thread_priority_change.c</t>
         </is>
       </c>
@@ -38726,13 +38726,13 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -38860,9 +38860,9 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_activate.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_activate.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_activate.c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -38872,12 +38872,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -38939,11 +38939,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
 Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -39007,9 +39007,9 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -39063,10 +39063,10 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_get.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_mutex_get.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_mutex_get.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -39076,12 +39076,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -39156,10 +39156,10 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
-Pointer Out of Bound
+          <t>Pointer Out of Bound
+Arbitrary memory write vulnerability (V0)
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Arbitrary memory write vulnerability (V0)
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
         </is>
       </c>
@@ -39207,16 +39207,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_flush.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_flush.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_queue_flush.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_queue_flush.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -39226,12 +39226,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -39287,9 +39287,9 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_set.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_set.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -39299,13 +39299,13 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
+Potential Function pointer dereference vulnerability
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Potential Function pointer dereference vulnerability</t>
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -39394,9 +39394,9 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_get.c
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_event_flags_get.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_suspend.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_activate.c
 /home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_event_flags_get.c</t>
         </is>
       </c>
@@ -39407,13 +39407,13 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (unlimited)
+          <t>Limited memory write vulnerability (V1)
+Pointer Out of Bound
 Information leak vulnerability (limited)
-Pointer Out of Bound
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)
-Limited memory write vulnerability(Uninitialized pointer dereference) (V2)</t>
+Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
+Information leak vulnerability (unlimited)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -39481,9 +39481,9 @@
       <c r="C58" t="inlineStr">
         <is>
           <t>Arbitrary memory write vulnerability (V0)
-Information leak vulnerability (limited)
+Uninitialized pointer dereference(read) vulnerability
 Limited memory write vulnerability(Uninitialized pointer dereference) (V2)
-Uninitialized pointer dereference(read) vulnerability</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -39538,8 +39538,8 @@
       <c r="A59" t="inlineStr">
         <is>
           <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_semaphore_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_delete.c</t>
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_semaphore_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_thread_system_resume.c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -39549,11 +39549,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Pointer Out of Bound
+Information leak vulnerability (limited)
 Limited memory write vulnerability (V3)
-Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Uninitialized pointer dereference(read) vulnerability</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -39597,9 +39597,9 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_delete.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c
-/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_delete.c</t>
+          <t>/home/klee/klee_src/test-rtos/threadx-5.3//common/src/txe_timer_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_delete.c
+/home/klee/klee_src/test-rtos/threadx-5.3//common/src/tx_timer_system_deactivate.c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -39609,10 +39609,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Information leak vulnerability (limited)
+          <t>Limited memory write vulnerability (V1)
 Limited memory write vulnerability (V3)
 Uninitialized pointer dereference(read) vulnerability
-Limited memory write vulnerability (V1)</t>
+Information leak vulnerability (limited)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -39669,7 +39669,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>I:0 II:24 X:35</t>
+          <t>I:8 II:16 X:35</t>
         </is>
       </c>
     </row>
